--- a/survey_templates/049_invitation_negative_answer_survey--survey_templates.xlsx
+++ b/survey_templates/049_invitation_negative_answer_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_title</t>
+          <t>invitation_denial_reason</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invitation Negative Answer Survey</t>
+          <t>Reason for Invitation Denial</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>invitation_sender</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Invitation Source</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>first_denial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>First Denial</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>still_want_to_attend</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Why are you denied the invitation?</t>
+          <t>Still Want to Attend</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>event_interest</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Are you denied the invitation because of a conflict with another event?</t>
+          <t>Event Interest</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>more_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Are you denied the invitation because of a conflict with another event?</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>more_info2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Are you denied the invitation because of a conflict with another event?</t>
+          <t>More Info2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>more_info3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the main reason you were denied the invitation?</t>
+          <t>More Info3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>more_info4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Do you have any other comments about why you were denied the invitation?</t>
+          <t>More Info4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>more_info5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Do you have any other comments about the invitation?</t>
+          <t>More Info5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>more_info6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Was the invitation offered to you by a person or a system?</t>
+          <t>More Info6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>more_info7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Was this the first time you were denied an invitation to this event?</t>
+          <t>More Info7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>more_info8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Would you still like to attend the event?</t>
+          <t>More Info8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>more_info9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Is this event something you are interested in?</t>
+          <t>More Info9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>more_info10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Is this event something you are interested in?</t>
+          <t>More Info10</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_15</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Would you like to provide more information about why you were denied the invitation?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,323 +896,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>invitation_sender_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'a)_i_am_not_able_to_attend',_'value':_'a'}</t>
+          <t>person</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'A) I am not able to attend', 'value': 'A'}</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>invitation_sender_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'b)_another_event_conflicts_with_the_invitation',_'value':_'b'}</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'B) Another event conflicts with the invitation', 'value': 'B'}</t>
+          <t>System</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>first_denial_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'c)_no_response',_'value':_'c'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'C) No response', 'value': 'C'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>first_denial_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'a)_i_am_not_able_to_attend',_'value':_'a'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'A) I am not able to attend', 'value': 'A'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>still_want_to_attend_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'b)_another_event_conflicts_with_the_invitation',_'value':_'b'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'B) Another event conflicts with the invitation', 'value': 'B'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>still_want_to_attend_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'c)_no_response',_'value':_'c'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'C) No response', 'value': 'C'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>event_interest_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'a)_i_am_not_able_to_attend',_'value':_'a'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'A) I am not able to attend', 'value': 'A'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>event_interest_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'b)_another_event_conflicts_with_the_invitation',_'value':_'b'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'B) Another event conflicts with the invitation', 'value': 'B'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>question_4_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'label':_'c)_no_response',_'value':_'c'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'C) No response', 'value': 'C'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'a)_person',_'value':_'person'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': 'A) Person', 'value': 'person'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'b)_system',_'value':_'system'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'B) System', 'value': 'system'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'label':_'a)_yes',_'value':_'a'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'label': 'A) Yes', 'value': 'A'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'label':_false,_'value':_'b'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'label': False, 'value': 'B'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_'a)_yes',_'value':_'a'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': 'A) Yes', 'value': 'A'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_false,_'value':_'b'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': False, 'value': 'B'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'label':_'a)_yes',_'value':_'a'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'label': 'A) Yes', 'value': 'A'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'label':_false,_'value':_'b'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'label': False, 'value': 'B'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_'a)_yes',_'value':_'a'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': 'A) Yes', 'value': 'A'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'label':_false,_'value':_'b'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'label': False, 'value': 'B'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
